--- a/input/validation/10-5/instance-7.xlsx
+++ b/input/validation/10-5/instance-7.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,7 +514,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -543,10 +543,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -576,25 +576,25 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -624,25 +624,25 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>40.8</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="J4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -672,58 +672,58 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>40.8</v>
+        <v>9.333333333333332</v>
       </c>
       <c r="I5" t="n">
-        <v>59.13333333333333</v>
+        <v>24.58333333333333</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>17</v>
+      </c>
+      <c r="M5" t="n">
         <v>16</v>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J-0</t>
+          <t>J-1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>O-04</t>
+          <t>O-10</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>4</v>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>4</v>
       </c>
-      <c r="H6" t="n">
-        <v>59.13333333333333</v>
-      </c>
       <c r="I6" t="n">
-        <v>75.13333333333333</v>
+        <v>21</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -751,42 +751,42 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>O-10</t>
+          <t>O-11</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I7" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>12</v>
+      </c>
+      <c r="L7" t="n">
         <v>13</v>
       </c>
-      <c r="I7" t="n">
-        <v>32</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>18</v>
-      </c>
-      <c r="L7" t="n">
-        <v>18</v>
-      </c>
       <c r="M7" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -799,42 +799,42 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>O-11</t>
+          <t>O-12</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>32</v>
+        <v>34.25</v>
       </c>
       <c r="I8" t="n">
-        <v>41.2</v>
+        <v>50.25</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -847,42 +847,42 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>O-12</t>
+          <t>O-13</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>41.2</v>
+        <v>50.25</v>
       </c>
       <c r="I9" t="n">
-        <v>61.2</v>
+        <v>55.58333333333334</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -895,82 +895,82 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>O-13</t>
+          <t>O-14</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>61.2</v>
+        <v>55.58333333333334</v>
       </c>
       <c r="I10" t="n">
-        <v>74.8</v>
+        <v>59.58333333333334</v>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J-1</t>
+          <t>J-2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>O-14</t>
+          <t>O-20</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>9</v>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>11</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>4</v>
       </c>
-      <c r="H11" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="I11" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
@@ -978,55 +978,55 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J-1</t>
+          <t>J-2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>O-15</t>
+          <t>O-21</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>83.8</v>
+        <v>11</v>
       </c>
       <c r="I12" t="n">
-        <v>99.55</v>
+        <v>31</v>
       </c>
       <c r="J12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -1039,42 +1039,42 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>O-20</t>
+          <t>O-22</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I13" t="n">
-        <v>37.4</v>
+        <v>40</v>
       </c>
       <c r="J13" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -1087,33 +1087,33 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>O-21</t>
+          <t>O-23</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>37.4</v>
+        <v>40</v>
       </c>
       <c r="I14" t="n">
-        <v>54.4</v>
+        <v>47</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1135,90 +1135,90 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>O-22</t>
+          <t>O-24</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>54.4</v>
+        <v>47</v>
       </c>
       <c r="I15" t="n">
-        <v>65.90000000000001</v>
+        <v>60.75</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J-2</t>
+          <t>J-3</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>O-23</t>
+          <t>O-30</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>65.90000000000001</v>
+        <v>14</v>
       </c>
       <c r="I16" t="n">
-        <v>82.40000000000001</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1231,42 +1231,42 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>O-30</t>
+          <t>O-31</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>21</v>
       </c>
       <c r="I17" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1279,42 +1279,42 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>O-31</t>
+          <t>O-32</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
+        <v>23</v>
+      </c>
+      <c r="I18" t="n">
         <v>27</v>
       </c>
-      <c r="I18" t="n">
-        <v>45</v>
-      </c>
       <c r="J18" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1327,42 +1327,42 @@
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>O-32</t>
+          <t>O-33</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I19" t="n">
-        <v>66.33333333333333</v>
+        <v>29</v>
       </c>
       <c r="J19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1375,87 +1375,87 @@
         <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D20" t="n">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>O-33</t>
+          <t>O-34</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" t="n">
-        <v>66.33333333333333</v>
+        <v>29</v>
       </c>
       <c r="I20" t="n">
-        <v>79.33333333333333</v>
+        <v>49.66666666666667</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J-3</t>
+          <t>J-4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D21" t="n">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>O-34</t>
+          <t>O-40</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>19</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>79.33333333333333</v>
+        <v>19</v>
       </c>
       <c r="I21" t="n">
-        <v>94.33333333333333</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1464,49 +1464,49 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J-3</t>
+          <t>J-4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>O-35</t>
+          <t>O-41</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>20</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>94.33333333333333</v>
+        <v>20</v>
       </c>
       <c r="I22" t="n">
-        <v>97.33333333333333</v>
+        <v>36.4</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -1519,42 +1519,42 @@
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D23" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>O-40</t>
+          <t>O-42</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>21</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>23</v>
+        <v>36.4</v>
       </c>
       <c r="I23" t="n">
-        <v>36.33333333333334</v>
+        <v>44.2</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K23" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M23" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N23" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1567,186 +1567,186 @@
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D24" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>O-41</t>
+          <t>O-43</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>36.33333333333334</v>
+        <v>44.2</v>
       </c>
       <c r="I24" t="n">
-        <v>51.93333333333334</v>
+        <v>46.2</v>
       </c>
       <c r="J24" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J-4</t>
+          <t>J-5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D25" t="n">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>O-42</t>
+          <t>O-50</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>51.93333333333334</v>
+        <v>25</v>
       </c>
       <c r="I25" t="n">
-        <v>57.26666666666667</v>
+        <v>43</v>
       </c>
       <c r="J25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J-4</t>
+          <t>J-5</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D26" t="n">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>O-43</t>
+          <t>O-51</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>57.26666666666667</v>
+        <v>43</v>
       </c>
       <c r="I26" t="n">
-        <v>70.26666666666668</v>
+        <v>56</v>
       </c>
       <c r="J26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>13</v>
       </c>
       <c r="L26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>J-4</t>
+          <t>J-5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D27" t="n">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>O-44</t>
+          <t>O-52</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>70.26666666666668</v>
+        <v>56</v>
       </c>
       <c r="I27" t="n">
-        <v>87.01666666666668</v>
+        <v>72</v>
       </c>
       <c r="J27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N27" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1759,42 +1759,42 @@
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D28" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>O-50</t>
+          <t>O-53</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="I28" t="n">
-        <v>43.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K28" t="n">
+        <v>13</v>
+      </c>
+      <c r="L28" t="n">
+        <v>19</v>
+      </c>
+      <c r="M28" t="n">
+        <v>13</v>
+      </c>
+      <c r="N28" t="n">
         <v>15</v>
-      </c>
-      <c r="L28" t="n">
-        <v>16</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1807,219 +1807,219 @@
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D29" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>O-51</t>
+          <t>O-54</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>27</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
-        <v>43.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>45.5</v>
+        <v>103.6</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>J-5</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D30" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>O-52</t>
+          <t>O-60</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>45.5</v>
+        <v>29</v>
       </c>
       <c r="I30" t="n">
-        <v>56.5</v>
+        <v>51</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K30" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="L30" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="M30" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>J-5</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D31" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>O-53</t>
+          <t>O-61</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>29</v>
       </c>
       <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>51</v>
+      </c>
+      <c r="I31" t="n">
+        <v>54</v>
+      </c>
+      <c r="J31" t="n">
         <v>3</v>
       </c>
-      <c r="H31" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="I31" t="n">
-        <v>73</v>
-      </c>
-      <c r="J31" t="n">
-        <v>17</v>
-      </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>J-5</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D32" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>O-54</t>
+          <t>O-62</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>30</v>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="I32" t="n">
-        <v>90.5</v>
+        <v>65.25</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L32" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M32" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>J-5</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D33" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>O-55</t>
+          <t>O-63</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>31</v>
       </c>
       <c r="G33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H33" t="n">
-        <v>90.5</v>
+        <v>65.25</v>
       </c>
       <c r="I33" t="n">
-        <v>106.5</v>
+        <v>83.75</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2028,13 +2028,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M33" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -2047,42 +2047,42 @@
         <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D34" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>O-60</t>
+          <t>O-64</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>32</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H34" t="n">
-        <v>33</v>
+        <v>83.75</v>
       </c>
       <c r="I34" t="n">
-        <v>37</v>
+        <v>89.75</v>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -2095,33 +2095,33 @@
         <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D35" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>O-61</t>
+          <t>O-65</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>33</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H35" t="n">
-        <v>37</v>
+        <v>89.75</v>
       </c>
       <c r="I35" t="n">
-        <v>50</v>
+        <v>97.75</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2130,151 +2130,151 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>J-6</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D36" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>O-62</t>
+          <t>O-70</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>34</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="I36" t="n">
-        <v>65.5</v>
+        <v>42.8</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K36" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M36" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>J-6</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C37" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D37" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>O-63</t>
+          <t>O-71</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>35</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>65.5</v>
+        <v>42.8</v>
       </c>
       <c r="I37" t="n">
-        <v>83.5</v>
+        <v>58.05</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K37" t="n">
         <v>19</v>
       </c>
       <c r="L37" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>J-6</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D38" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>O-64</t>
+          <t>O-72</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>36</v>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>83.5</v>
+        <v>58.05</v>
       </c>
       <c r="I38" t="n">
-        <v>95.5</v>
+        <v>59.05</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2287,36 +2287,36 @@
         <v>7</v>
       </c>
       <c r="C39" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D39" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>O-70</t>
+          <t>O-73</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>37</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>34</v>
+        <v>59.05</v>
       </c>
       <c r="I39" t="n">
-        <v>48</v>
+        <v>71.71666666666667</v>
       </c>
       <c r="J39" t="n">
+        <v>12</v>
+      </c>
+      <c r="K39" t="n">
         <v>14</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2335,39 +2335,39 @@
         <v>7</v>
       </c>
       <c r="C40" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D40" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>O-71</t>
+          <t>O-74</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>38</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H40" t="n">
-        <v>48</v>
+        <v>71.71666666666667</v>
       </c>
       <c r="I40" t="n">
-        <v>64.5</v>
+        <v>87.71666666666667</v>
       </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>15</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -2376,142 +2376,142 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C41" t="n">
         <v>34</v>
       </c>
       <c r="D41" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>O-72</t>
+          <t>O-80</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>39</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>64.5</v>
+        <v>34</v>
       </c>
       <c r="I41" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L41" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="M41" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C42" t="n">
         <v>34</v>
       </c>
       <c r="D42" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>O-73</t>
+          <t>O-81</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>40</v>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="I42" t="n">
-        <v>83.33333333333333</v>
+        <v>72</v>
       </c>
       <c r="J42" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M42" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C43" t="n">
         <v>34</v>
       </c>
       <c r="D43" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>O-74</t>
+          <t>O-82</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>41</v>
       </c>
       <c r="G43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
-        <v>83.33333333333333</v>
+        <v>72</v>
       </c>
       <c r="I43" t="n">
-        <v>88.66666666666666</v>
+        <v>88</v>
       </c>
       <c r="J43" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L43" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -2520,49 +2520,49 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C44" t="n">
         <v>34</v>
       </c>
       <c r="D44" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>O-75</t>
+          <t>O-83</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>42</v>
       </c>
       <c r="G44" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" t="n">
+        <v>88</v>
+      </c>
+      <c r="I44" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>5</v>
       </c>
-      <c r="H44" t="n">
-        <v>88.66666666666666</v>
-      </c>
-      <c r="I44" t="n">
-        <v>98.86666666666666</v>
-      </c>
-      <c r="J44" t="n">
-        <v>8</v>
-      </c>
-      <c r="K44" t="n">
-        <v>12</v>
-      </c>
-      <c r="L44" t="n">
-        <v>12</v>
-      </c>
-      <c r="M44" t="n">
-        <v>9</v>
-      </c>
       <c r="N44" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -2575,42 +2575,42 @@
         <v>8</v>
       </c>
       <c r="C45" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D45" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>O-80</t>
+          <t>O-84</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>43</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H45" t="n">
-        <v>37</v>
+        <v>93.5</v>
       </c>
       <c r="I45" t="n">
-        <v>52.5</v>
+        <v>95.5</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2623,132 +2623,132 @@
         <v>8</v>
       </c>
       <c r="C46" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D46" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>O-81</t>
+          <t>O-85</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>44</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H46" t="n">
-        <v>52.5</v>
+        <v>95.5</v>
       </c>
       <c r="I46" t="n">
-        <v>69.25</v>
+        <v>114.5</v>
       </c>
       <c r="J46" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K46" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L46" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M46" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-9</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C47" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D47" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>O-82</t>
+          <t>O-90</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>45</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>69.25</v>
+        <v>35</v>
       </c>
       <c r="I47" t="n">
-        <v>77.25</v>
+        <v>40.66666666666666</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M47" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-9</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C48" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D48" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>O-83</t>
+          <t>O-91</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>77.25</v>
+        <v>40.66666666666666</v>
       </c>
       <c r="I48" t="n">
-        <v>86.25</v>
+        <v>58.16666666666666</v>
       </c>
       <c r="J48" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L48" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -2760,97 +2760,97 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-9</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C49" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D49" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>O-84</t>
+          <t>O-92</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>47</v>
       </c>
       <c r="G49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
-        <v>86.25</v>
+        <v>58.16666666666666</v>
       </c>
       <c r="I49" t="n">
-        <v>98.45</v>
+        <v>76.56666666666666</v>
       </c>
       <c r="J49" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K49" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L49" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="M49" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N49" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-9</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C50" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D50" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>O-85</t>
+          <t>O-93</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>48</v>
       </c>
       <c r="G50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H50" t="n">
-        <v>98.45</v>
+        <v>76.56666666666666</v>
       </c>
       <c r="I50" t="n">
-        <v>107.45</v>
+        <v>84.31666666666666</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K50" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
@@ -2863,39 +2863,39 @@
         <v>9</v>
       </c>
       <c r="C51" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D51" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>O-90</t>
+          <t>O-94</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>49</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H51" t="n">
-        <v>38</v>
+        <v>84.31666666666666</v>
       </c>
       <c r="I51" t="n">
-        <v>42</v>
+        <v>88.81666666666666</v>
       </c>
       <c r="J51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
         <v>4</v>
@@ -2911,234 +2911,42 @@
         <v>9</v>
       </c>
       <c r="C52" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D52" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>O-91</t>
+          <t>O-95</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>50</v>
       </c>
       <c r="G52" t="n">
+        <v>5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>88.81666666666666</v>
+      </c>
+      <c r="I52" t="n">
+        <v>89.81666666666666</v>
+      </c>
+      <c r="J52" t="n">
         <v>1</v>
       </c>
-      <c r="H52" t="n">
-        <v>42</v>
-      </c>
-      <c r="I52" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="J52" t="n">
-        <v>10</v>
-      </c>
       <c r="K52" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>J-9</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>9</v>
-      </c>
-      <c r="C53" t="n">
-        <v>38</v>
-      </c>
-      <c r="D53" t="n">
-        <v>80</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>O-92</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>51</v>
-      </c>
-      <c r="G53" t="n">
-        <v>2</v>
-      </c>
-      <c r="H53" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="I53" t="n">
-        <v>68.34999999999999</v>
-      </c>
-      <c r="J53" t="n">
-        <v>14</v>
-      </c>
-      <c r="K53" t="n">
-        <v>15</v>
-      </c>
-      <c r="L53" t="n">
-        <v>16</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>J-9</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>9</v>
-      </c>
-      <c r="C54" t="n">
-        <v>38</v>
-      </c>
-      <c r="D54" t="n">
-        <v>80</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>O-93</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>52</v>
-      </c>
-      <c r="G54" t="n">
-        <v>3</v>
-      </c>
-      <c r="H54" t="n">
-        <v>68.34999999999999</v>
-      </c>
-      <c r="I54" t="n">
-        <v>70.34999999999999</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>J-9</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>9</v>
-      </c>
-      <c r="C55" t="n">
-        <v>38</v>
-      </c>
-      <c r="D55" t="n">
-        <v>80</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>O-94</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>53</v>
-      </c>
-      <c r="G55" t="n">
-        <v>4</v>
-      </c>
-      <c r="H55" t="n">
-        <v>70.34999999999999</v>
-      </c>
-      <c r="I55" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="J55" t="n">
-        <v>9</v>
-      </c>
-      <c r="K55" t="n">
-        <v>9</v>
-      </c>
-      <c r="L55" t="n">
-        <v>9</v>
-      </c>
-      <c r="M55" t="n">
-        <v>10</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>J-9</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>9</v>
-      </c>
-      <c r="C56" t="n">
-        <v>38</v>
-      </c>
-      <c r="D56" t="n">
-        <v>80</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>O-95</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>54</v>
-      </c>
-      <c r="G56" t="n">
-        <v>5</v>
-      </c>
-      <c r="H56" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="I56" t="n">
-        <v>98.39999999999999</v>
-      </c>
-      <c r="J56" t="n">
-        <v>19</v>
-      </c>
-      <c r="K56" t="n">
-        <v>21</v>
-      </c>
-      <c r="L56" t="n">
-        <v>20</v>
-      </c>
-      <c r="M56" t="n">
-        <v>17</v>
-      </c>
-      <c r="N56" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3152,7 +2960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3226,541 +3034,6 @@
           <t>Machine 4</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Initial_Machine</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>J-5</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>28</v>
-      </c>
-      <c r="D2" t="n">
-        <v>99</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>O-53</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>29</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H2" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J2" t="n">
-        <v>17</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Machine 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>J-0</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>93</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>O-04</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H3" t="n">
-        <v>59.13333333333333</v>
-      </c>
-      <c r="I3" t="n">
-        <v>75.13333333333333</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Machine 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>J-1</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>13</v>
-      </c>
-      <c r="D4" t="n">
-        <v>116</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>O-13</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K4" t="n">
-        <v>14</v>
-      </c>
-      <c r="L4" t="n">
-        <v>14</v>
-      </c>
-      <c r="M4" t="n">
-        <v>11</v>
-      </c>
-      <c r="N4" t="n">
-        <v>14</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Machine 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>J-6</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>33</v>
-      </c>
-      <c r="D5" t="n">
-        <v>79</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>O-63</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>35</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>19</v>
-      </c>
-      <c r="L5" t="n">
-        <v>17</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>18</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Machine 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>J-2</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>18</v>
-      </c>
-      <c r="D6" t="n">
-        <v>82</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>O-23</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>13</v>
-      </c>
-      <c r="L6" t="n">
-        <v>19</v>
-      </c>
-      <c r="M6" t="n">
-        <v>17</v>
-      </c>
-      <c r="N6" t="n">
-        <v>17</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Machine 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>J-3</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>21</v>
-      </c>
-      <c r="D7" t="n">
-        <v>98</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>O-33</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>18</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>66.33333333333333</v>
-      </c>
-      <c r="I7" t="n">
-        <v>79.33333333333333</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>13</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Buffer</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>J-8</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>8</v>
-      </c>
-      <c r="C8" t="n">
-        <v>37</v>
-      </c>
-      <c r="D8" t="n">
-        <v>98</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>O-82</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>45</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>69.25</v>
-      </c>
-      <c r="I8" t="n">
-        <v>77.25</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>9</v>
-      </c>
-      <c r="N8" t="n">
-        <v>7</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Buffer</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>J-4</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>23</v>
-      </c>
-      <c r="D9" t="n">
-        <v>85</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>O-44</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>25</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>70.26666666666668</v>
-      </c>
-      <c r="I9" t="n">
-        <v>87.01666666666668</v>
-      </c>
-      <c r="J9" t="n">
-        <v>17</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>17</v>
-      </c>
-      <c r="M9" t="n">
-        <v>18</v>
-      </c>
-      <c r="N9" t="n">
-        <v>15</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Buffer</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>J-9</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>9</v>
-      </c>
-      <c r="C10" t="n">
-        <v>38</v>
-      </c>
-      <c r="D10" t="n">
-        <v>80</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>O-94</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>53</v>
-      </c>
-      <c r="G10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>70.34999999999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="J10" t="n">
-        <v>9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>9</v>
-      </c>
-      <c r="L10" t="n">
-        <v>9</v>
-      </c>
-      <c r="M10" t="n">
-        <v>10</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Buffer</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>J-7</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>7</v>
-      </c>
-      <c r="C11" t="n">
-        <v>34</v>
-      </c>
-      <c r="D11" t="n">
-        <v>85</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>O-73</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>40</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>71</v>
-      </c>
-      <c r="I11" t="n">
-        <v>83.33333333333333</v>
-      </c>
-      <c r="J11" t="n">
-        <v>12</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>11</v>
-      </c>
-      <c r="N11" t="n">
-        <v>14</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Buffer</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/input/validation/10-5/instance-7.xlsx
+++ b/input/validation/10-5/instance-7.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,7 +514,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -531,10 +531,10 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -543,10 +543,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -576,25 +576,25 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -624,25 +624,25 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="I4" t="n">
-        <v>9.333333333333332</v>
+        <v>21.33333333333334</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -672,25 +672,25 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>9.333333333333332</v>
+        <v>21.33333333333334</v>
       </c>
       <c r="I5" t="n">
-        <v>24.58333333333333</v>
+        <v>37.33333333333334</v>
       </c>
       <c r="J5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -703,10 +703,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -720,25 +720,25 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>21</v>
+        <v>23.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -751,10 +751,10 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -768,25 +768,25 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>21</v>
+        <v>23.6</v>
       </c>
       <c r="I7" t="n">
-        <v>34.25</v>
+        <v>35.35</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>12</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" t="n">
         <v>13</v>
-      </c>
-      <c r="M7" t="n">
-        <v>12</v>
-      </c>
-      <c r="N7" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -816,25 +816,25 @@
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>34.25</v>
+        <v>35.35</v>
       </c>
       <c r="I8" t="n">
-        <v>50.25</v>
+        <v>43.6</v>
       </c>
       <c r="J8" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -847,10 +847,10 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -864,25 +864,25 @@
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>50.25</v>
+        <v>43.6</v>
       </c>
       <c r="I9" t="n">
-        <v>55.58333333333334</v>
+        <v>46.6</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -912,22 +912,22 @@
         <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>55.58333333333334</v>
+        <v>46.6</v>
       </c>
       <c r="I10" t="n">
-        <v>59.58333333333334</v>
+        <v>50.6</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
@@ -936,49 +936,49 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J-2</t>
+          <t>J-1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>O-20</t>
+          <t>O-15</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>50.6</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -991,42 +991,42 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
         <v>67</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>O-21</t>
+          <t>O-20</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I12" t="n">
-        <v>31</v>
+        <v>22.5</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N12" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1039,27 +1039,27 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
         <v>67</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>O-22</t>
+          <t>O-21</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>31</v>
+        <v>22.5</v>
       </c>
       <c r="I13" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -1087,42 +1087,42 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
         <v>67</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>O-23</t>
+          <t>O-22</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="I14" t="n">
-        <v>47</v>
+        <v>46.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1135,138 +1135,138 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D15" t="n">
         <v>67</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>O-24</t>
+          <t>O-23</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>47</v>
+        <v>46.5</v>
       </c>
       <c r="I15" t="n">
-        <v>60.75</v>
+        <v>58.83333333333334</v>
       </c>
       <c r="J15" t="n">
         <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J-3</t>
+          <t>J-2</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>O-30</t>
+          <t>O-24</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>14</v>
+        <v>58.83333333333334</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>61.83333333333334</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J-3</t>
+          <t>J-2</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>O-31</t>
+          <t>O-25</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>21</v>
+        <v>61.83333333333334</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>67.08333333333334</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -1279,39 +1279,39 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>O-32</t>
+          <t>O-30</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I18" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1327,27 +1327,27 @@
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>O-33</t>
+          <t>O-31</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I19" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1356,13 +1356,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1375,87 +1375,87 @@
         <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>O-34</t>
+          <t>O-32</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="I20" t="n">
-        <v>49.66666666666667</v>
+        <v>54.25</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K20" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>15</v>
+      </c>
+      <c r="N20" t="n">
         <v>20</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J-4</t>
+          <t>J-3</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D21" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>O-40</t>
+          <t>O-33</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>19</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>19</v>
+        <v>54.25</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>69.58333333333333</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1471,42 +1471,42 @@
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>O-41</t>
+          <t>O-40</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>20</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I22" t="n">
-        <v>36.4</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L22" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1519,42 +1519,42 @@
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>O-42</t>
+          <t>O-41</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>21</v>
       </c>
       <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>26</v>
+      </c>
+      <c r="I23" t="n">
+        <v>28</v>
+      </c>
+      <c r="J23" t="n">
         <v>2</v>
       </c>
-      <c r="H23" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="I23" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>9</v>
-      </c>
       <c r="K23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1567,90 +1567,90 @@
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>O-43</t>
+          <t>O-42</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>44.2</v>
+        <v>28</v>
       </c>
       <c r="I24" t="n">
-        <v>46.2</v>
+        <v>47</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J-5</t>
+          <t>J-4</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>O-50</t>
+          <t>O-43</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I25" t="n">
-        <v>43</v>
+        <v>58.75</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N25" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1663,24 +1663,24 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D26" t="n">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>O-51</t>
+          <t>O-50</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I26" t="n">
         <v>56</v>
@@ -1689,10 +1689,10 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L26" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -1711,42 +1711,42 @@
         <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D27" t="n">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>O-52</t>
+          <t>O-51</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
         <v>56</v>
       </c>
       <c r="I27" t="n">
-        <v>72</v>
+        <v>60.5</v>
       </c>
       <c r="J27" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -1759,42 +1759,42 @@
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>O-53</t>
+          <t>O-52</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>72</v>
+        <v>60.5</v>
       </c>
       <c r="I28" t="n">
-        <v>86.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="J28" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="L28" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
@@ -1807,42 +1807,42 @@
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D29" t="n">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>O-54</t>
+          <t>O-53</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>27</v>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>86.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="I29" t="n">
-        <v>103.6</v>
+        <v>79.5</v>
       </c>
       <c r="J29" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="L29" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1855,10 +1855,10 @@
         <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D30" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1872,25 +1872,25 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I30" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J30" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -1903,10 +1903,10 @@
         <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D31" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1920,25 +1920,25 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I31" t="n">
-        <v>54</v>
+        <v>66.2</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -1951,10 +1951,10 @@
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D32" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1968,25 +1968,25 @@
         <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>54</v>
+        <v>66.2</v>
       </c>
       <c r="I32" t="n">
-        <v>65.25</v>
+        <v>68.2</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1999,10 +1999,10 @@
         <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D33" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2016,112 +2016,112 @@
         <v>3</v>
       </c>
       <c r="H33" t="n">
-        <v>65.25</v>
+        <v>68.2</v>
       </c>
       <c r="I33" t="n">
-        <v>83.75</v>
+        <v>70.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>J-6</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C34" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D34" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>O-64</t>
+          <t>O-70</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>32</v>
       </c>
       <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>39</v>
+      </c>
+      <c r="I34" t="n">
+        <v>43</v>
+      </c>
+      <c r="J34" t="n">
         <v>4</v>
       </c>
-      <c r="H34" t="n">
-        <v>83.75</v>
-      </c>
-      <c r="I34" t="n">
-        <v>89.75</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
       <c r="K34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>J-6</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C35" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D35" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>O-65</t>
+          <t>O-71</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>33</v>
       </c>
       <c r="G35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>89.75</v>
+        <v>43</v>
       </c>
       <c r="I35" t="n">
-        <v>97.75</v>
+        <v>51.5</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2143,42 +2143,42 @@
         <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D36" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>O-70</t>
+          <t>O-72</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>34</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>31</v>
+        <v>51.5</v>
       </c>
       <c r="I36" t="n">
-        <v>42.8</v>
+        <v>64</v>
       </c>
       <c r="J36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L36" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2191,42 +2191,42 @@
         <v>7</v>
       </c>
       <c r="C37" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D37" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>O-71</t>
+          <t>O-73</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>35</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>42.8</v>
+        <v>64</v>
       </c>
       <c r="I37" t="n">
-        <v>58.05</v>
+        <v>79</v>
       </c>
       <c r="J37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
         <v>15</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="38">
@@ -2239,42 +2239,42 @@
         <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D38" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>O-72</t>
+          <t>O-74</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>36</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>58.05</v>
+        <v>79</v>
       </c>
       <c r="I38" t="n">
-        <v>59.05</v>
+        <v>93.5</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39">
@@ -2287,87 +2287,87 @@
         <v>7</v>
       </c>
       <c r="C39" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D39" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>O-73</t>
+          <t>O-75</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>37</v>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>59.05</v>
+        <v>93.5</v>
       </c>
       <c r="I39" t="n">
-        <v>71.71666666666667</v>
+        <v>108.1</v>
       </c>
       <c r="J39" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K39" t="n">
         <v>14</v>
       </c>
       <c r="L39" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C40" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D40" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>O-74</t>
+          <t>O-80</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>38</v>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>71.71666666666667</v>
+        <v>41</v>
       </c>
       <c r="I40" t="n">
-        <v>87.71666666666667</v>
+        <v>57</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M40" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -2383,42 +2383,42 @@
         <v>8</v>
       </c>
       <c r="C41" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D41" t="n">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>O-80</t>
+          <t>O-81</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>39</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="I41" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="J41" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
@@ -2431,27 +2431,27 @@
         <v>8</v>
       </c>
       <c r="C42" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D42" t="n">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>O-81</t>
+          <t>O-82</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>40</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="I42" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -2479,42 +2479,42 @@
         <v>8</v>
       </c>
       <c r="C43" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D43" t="n">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>O-82</t>
+          <t>O-83</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>41</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I43" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K43" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -2527,30 +2527,30 @@
         <v>8</v>
       </c>
       <c r="C44" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D44" t="n">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>O-83</t>
+          <t>O-84</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>42</v>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H44" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I44" t="n">
         <v>93.5</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2559,106 +2559,106 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="N44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-9</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C45" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D45" t="n">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>O-84</t>
+          <t>O-90</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>43</v>
       </c>
       <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>49</v>
+      </c>
+      <c r="I45" t="n">
+        <v>53</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
         <v>4</v>
       </c>
-      <c r="H45" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="I45" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2</v>
-      </c>
-      <c r="K45" t="n">
-        <v>2</v>
-      </c>
-      <c r="L45" t="n">
-        <v>2</v>
-      </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-9</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C46" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D46" t="n">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>O-85</t>
+          <t>O-91</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>44</v>
       </c>
       <c r="G46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>95.5</v>
+        <v>53</v>
       </c>
       <c r="I46" t="n">
-        <v>114.5</v>
+        <v>56</v>
       </c>
       <c r="J46" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="K46" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="L46" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="M46" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2671,39 +2671,39 @@
         <v>9</v>
       </c>
       <c r="C47" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D47" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>O-90</t>
+          <t>O-92</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>45</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I47" t="n">
-        <v>40.66666666666666</v>
+        <v>63</v>
       </c>
       <c r="J47" t="n">
         <v>7</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -2719,42 +2719,42 @@
         <v>9</v>
       </c>
       <c r="C48" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D48" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>O-91</t>
+          <t>O-93</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H48" t="n">
-        <v>40.66666666666666</v>
+        <v>63</v>
       </c>
       <c r="I48" t="n">
-        <v>58.16666666666666</v>
+        <v>80.5</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
@@ -2767,42 +2767,42 @@
         <v>9</v>
       </c>
       <c r="C49" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D49" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>O-92</t>
+          <t>O-94</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>47</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H49" t="n">
-        <v>58.16666666666666</v>
+        <v>80.5</v>
       </c>
       <c r="I49" t="n">
-        <v>76.56666666666666</v>
+        <v>98.25</v>
       </c>
       <c r="J49" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L49" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N49" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50">
@@ -2815,138 +2815,42 @@
         <v>9</v>
       </c>
       <c r="C50" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D50" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>O-93</t>
+          <t>O-95</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>48</v>
       </c>
       <c r="G50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H50" t="n">
-        <v>76.56666666666666</v>
+        <v>98.25</v>
       </c>
       <c r="I50" t="n">
-        <v>84.31666666666666</v>
+        <v>112.25</v>
       </c>
       <c r="J50" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M50" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="N50" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>J-9</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>9</v>
-      </c>
-      <c r="C51" t="n">
-        <v>35</v>
-      </c>
-      <c r="D51" t="n">
-        <v>74</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>O-94</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>49</v>
-      </c>
-      <c r="G51" t="n">
-        <v>4</v>
-      </c>
-      <c r="H51" t="n">
-        <v>84.31666666666666</v>
-      </c>
-      <c r="I51" t="n">
-        <v>88.81666666666666</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>5</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>J-9</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>9</v>
-      </c>
-      <c r="C52" t="n">
-        <v>35</v>
-      </c>
-      <c r="D52" t="n">
-        <v>74</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>O-95</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>50</v>
-      </c>
-      <c r="G52" t="n">
-        <v>5</v>
-      </c>
-      <c r="H52" t="n">
-        <v>88.81666666666666</v>
-      </c>
-      <c r="I52" t="n">
-        <v>89.81666666666666</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/input/validation/10-5/instance-7.xlsx
+++ b/input/validation/10-5/instance-7.xlsx
@@ -514,7 +514,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -531,22 +531,22 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>11.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -576,25 +576,25 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>11.2</v>
       </c>
       <c r="I3" t="n">
-        <v>10.33333333333333</v>
+        <v>22.2</v>
       </c>
       <c r="J3" t="n">
+        <v>12</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M3" t="n">
         <v>10</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>9</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -624,25 +624,25 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>10.33333333333333</v>
+        <v>22.2</v>
       </c>
       <c r="I4" t="n">
-        <v>21.33333333333334</v>
+        <v>25.2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -672,10 +672,10 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>21.33333333333334</v>
+        <v>25.2</v>
       </c>
       <c r="I5" t="n">
-        <v>37.33333333333334</v>
+        <v>30.2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -684,13 +684,13 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -703,10 +703,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -720,25 +720,25 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>23.6</v>
+        <v>13.5</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -751,10 +751,10 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -768,25 +768,25 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>23.6</v>
+        <v>13.5</v>
       </c>
       <c r="I7" t="n">
-        <v>35.35</v>
+        <v>30.5</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M7" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="N7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -816,22 +816,22 @@
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>35.35</v>
+        <v>30.5</v>
       </c>
       <c r="I8" t="n">
-        <v>43.6</v>
+        <v>38</v>
       </c>
       <c r="J8" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>8</v>
       </c>
-      <c r="K8" t="n">
-        <v>9</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N8" t="n">
         <v>8</v>
@@ -847,10 +847,10 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -864,25 +864,25 @@
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>43.6</v>
+        <v>38</v>
       </c>
       <c r="I9" t="n">
-        <v>46.6</v>
+        <v>57.25</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -912,25 +912,25 @@
         <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>46.6</v>
+        <v>57.25</v>
       </c>
       <c r="I10" t="n">
-        <v>50.6</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -943,10 +943,10 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -960,25 +960,25 @@
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>50.6</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>71.09999999999999</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -991,10 +991,10 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1008,25 +1008,25 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" t="n">
         <v>15</v>
       </c>
-      <c r="I12" t="n">
-        <v>22.5</v>
-      </c>
       <c r="J12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -1039,10 +1039,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1056,25 +1056,25 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>22.5</v>
+        <v>15</v>
       </c>
       <c r="I13" t="n">
-        <v>42.5</v>
+        <v>19</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1087,10 +1087,10 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>42.5</v>
+        <v>19</v>
       </c>
       <c r="I14" t="n">
-        <v>46.5</v>
+        <v>26.5</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1135,10 +1135,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1152,25 +1152,25 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>46.5</v>
+        <v>26.5</v>
       </c>
       <c r="I15" t="n">
-        <v>58.83333333333334</v>
+        <v>34.5</v>
       </c>
       <c r="J15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1183,10 +1183,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1200,73 +1200,73 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>58.83333333333334</v>
+        <v>34.5</v>
       </c>
       <c r="I16" t="n">
-        <v>61.83333333333334</v>
+        <v>53.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J-2</t>
+          <t>J-3</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>O-25</t>
+          <t>O-30</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>61.83333333333334</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>67.08333333333334</v>
+        <v>21.6</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L17" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -1279,39 +1279,39 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>O-30</t>
+          <t>O-31</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>18</v>
+        <v>21.6</v>
       </c>
       <c r="I18" t="n">
-        <v>33</v>
+        <v>25.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1327,27 +1327,27 @@
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>O-31</t>
+          <t>O-32</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>33</v>
+        <v>25.6</v>
       </c>
       <c r="I19" t="n">
-        <v>37</v>
+        <v>40.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1359,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1375,90 +1375,90 @@
         <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>O-32</t>
+          <t>O-33</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>37</v>
+        <v>40.6</v>
       </c>
       <c r="I20" t="n">
-        <v>54.25</v>
+        <v>56.6</v>
       </c>
       <c r="J20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J-3</t>
+          <t>J-4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>O-33</t>
+          <t>O-40</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>19</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>54.25</v>
+        <v>9</v>
       </c>
       <c r="I21" t="n">
-        <v>69.58333333333333</v>
+        <v>15</v>
       </c>
       <c r="J21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -1471,42 +1471,42 @@
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>O-40</t>
+          <t>O-41</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>20</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="I22" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -1519,42 +1519,42 @@
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>O-41</t>
+          <t>O-42</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>21</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
+        <v>22</v>
+      </c>
+      <c r="I23" t="n">
         <v>26</v>
       </c>
-      <c r="I23" t="n">
-        <v>28</v>
-      </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1567,90 +1567,90 @@
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D24" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>O-42</t>
+          <t>O-43</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I24" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J-4</t>
+          <t>J-5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D25" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>O-43</t>
+          <t>O-50</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="I25" t="n">
-        <v>58.75</v>
+        <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
@@ -1663,42 +1663,42 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>O-50</t>
+          <t>O-51</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I26" t="n">
-        <v>56</v>
+        <v>33.8</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1711,42 +1711,42 @@
         <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D27" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>O-51</t>
+          <t>O-52</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>56</v>
+        <v>33.8</v>
       </c>
       <c r="I27" t="n">
-        <v>60.5</v>
+        <v>49</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
@@ -1759,42 +1759,42 @@
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>O-52</t>
+          <t>O-53</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>60.5</v>
+        <v>49</v>
       </c>
       <c r="I28" t="n">
-        <v>77.5</v>
+        <v>53</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1807,42 +1807,42 @@
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>O-53</t>
+          <t>O-54</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>27</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
-        <v>77.5</v>
+        <v>53</v>
       </c>
       <c r="I29" t="n">
-        <v>79.5</v>
+        <v>59</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1855,10 +1855,10 @@
         <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D30" t="n">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="I30" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1887,10 +1887,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1903,10 +1903,10 @@
         <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D31" t="n">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1920,25 +1920,25 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="I31" t="n">
-        <v>66.2</v>
+        <v>35.2</v>
       </c>
       <c r="J31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M31" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -1951,10 +1951,10 @@
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D32" t="n">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1968,25 +1968,25 @@
         <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>66.2</v>
+        <v>35.2</v>
       </c>
       <c r="I32" t="n">
-        <v>68.2</v>
+        <v>51.2</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
@@ -1999,10 +1999,10 @@
         <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D33" t="n">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2016,22 +2016,22 @@
         <v>3</v>
       </c>
       <c r="H33" t="n">
-        <v>68.2</v>
+        <v>51.2</v>
       </c>
       <c r="I33" t="n">
-        <v>70.2</v>
+        <v>69.45</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -2040,97 +2040,97 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D34" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>O-70</t>
+          <t>O-64</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>32</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H34" t="n">
-        <v>39</v>
+        <v>69.45</v>
       </c>
       <c r="I34" t="n">
-        <v>43</v>
+        <v>78.95</v>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L34" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D35" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>O-71</t>
+          <t>O-65</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>33</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H35" t="n">
-        <v>43</v>
+        <v>78.95</v>
       </c>
       <c r="I35" t="n">
-        <v>51.5</v>
+        <v>87.45</v>
       </c>
       <c r="J35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>9</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2143,42 +2143,42 @@
         <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D36" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>O-72</t>
+          <t>O-70</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>34</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>51.5</v>
+        <v>15</v>
       </c>
       <c r="I36" t="n">
-        <v>64</v>
+        <v>28.25</v>
       </c>
       <c r="J36" t="n">
+        <v>14</v>
+      </c>
+      <c r="K36" t="n">
         <v>11</v>
       </c>
-      <c r="K36" t="n">
-        <v>14</v>
-      </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
@@ -2191,34 +2191,34 @@
         <v>7</v>
       </c>
       <c r="C37" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D37" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>O-73</t>
+          <t>O-71</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>35</v>
       </c>
       <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="I37" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>3</v>
       </c>
-      <c r="H37" t="n">
-        <v>64</v>
-      </c>
-      <c r="I37" t="n">
-        <v>79</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2239,42 +2239,42 @@
         <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D38" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>O-74</t>
+          <t>O-72</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>36</v>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>79</v>
+        <v>31.25</v>
       </c>
       <c r="I38" t="n">
-        <v>93.5</v>
+        <v>44.25</v>
       </c>
       <c r="J38" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L38" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2287,135 +2287,135 @@
         <v>7</v>
       </c>
       <c r="C39" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D39" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>O-75</t>
+          <t>O-73</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>37</v>
       </c>
       <c r="G39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>93.5</v>
+        <v>44.25</v>
       </c>
       <c r="I39" t="n">
-        <v>108.1</v>
+        <v>45.25</v>
       </c>
       <c r="J39" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D40" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>O-80</t>
+          <t>O-74</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>38</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H40" t="n">
-        <v>41</v>
+        <v>45.25</v>
       </c>
       <c r="I40" t="n">
-        <v>57</v>
+        <v>50.05</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L40" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C41" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D41" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>O-81</t>
+          <t>O-75</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>39</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H41" t="n">
-        <v>57</v>
+        <v>50.05</v>
       </c>
       <c r="I41" t="n">
-        <v>69</v>
+        <v>60.05</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N41" t="n">
         <v>12</v>
@@ -2431,42 +2431,42 @@
         <v>8</v>
       </c>
       <c r="C42" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="D42" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>O-82</t>
+          <t>O-80</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>40</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="I42" t="n">
-        <v>74</v>
+        <v>28.5</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
@@ -2479,42 +2479,42 @@
         <v>8</v>
       </c>
       <c r="C43" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="D43" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>O-83</t>
+          <t>O-81</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>41</v>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>74</v>
+        <v>28.5</v>
       </c>
       <c r="I43" t="n">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="J43" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K43" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N43" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44">
@@ -2527,90 +2527,90 @@
         <v>8</v>
       </c>
       <c r="C44" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="D44" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>O-84</t>
+          <t>O-82</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>42</v>
       </c>
       <c r="G44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="I44" t="n">
-        <v>93.5</v>
+        <v>55.5</v>
       </c>
       <c r="J44" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M44" t="n">
+        <v>15</v>
+      </c>
+      <c r="N44" t="n">
         <v>13</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>J-9</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C45" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="D45" t="n">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>O-90</t>
+          <t>O-83</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>43</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
-        <v>49</v>
+        <v>55.5</v>
       </c>
       <c r="I45" t="n">
-        <v>53</v>
+        <v>57.5</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -2623,39 +2623,39 @@
         <v>9</v>
       </c>
       <c r="C46" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D46" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>O-91</t>
+          <t>O-90</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>44</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I46" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="J46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -2671,39 +2671,39 @@
         <v>9</v>
       </c>
       <c r="C47" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D47" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>O-92</t>
+          <t>O-91</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>45</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="I47" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="J47" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K47" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -2719,42 +2719,42 @@
         <v>9</v>
       </c>
       <c r="C48" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D48" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>O-93</t>
+          <t>O-92</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="I48" t="n">
-        <v>80.5</v>
+        <v>57.66666666666666</v>
       </c>
       <c r="J48" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="M48" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="N48" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
@@ -2767,42 +2767,42 @@
         <v>9</v>
       </c>
       <c r="C49" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D49" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>O-94</t>
+          <t>O-93</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>47</v>
       </c>
       <c r="G49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H49" t="n">
-        <v>80.5</v>
+        <v>57.66666666666666</v>
       </c>
       <c r="I49" t="n">
-        <v>98.25</v>
+        <v>65.66666666666666</v>
       </c>
       <c r="J49" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N49" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -2815,42 +2815,42 @@
         <v>9</v>
       </c>
       <c r="C50" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D50" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>O-95</t>
+          <t>O-94</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>48</v>
       </c>
       <c r="G50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H50" t="n">
-        <v>98.25</v>
+        <v>65.66666666666666</v>
       </c>
       <c r="I50" t="n">
-        <v>112.25</v>
+        <v>68.66666666666666</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
